--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="56">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -131,6 +131,54 @@
   </si>
   <si>
     <t>The search results page is shown again</t>
+  </si>
+  <si>
+    <t>TC-YT-005</t>
+  </si>
+  <si>
+    <t>Search results match the query</t>
+  </si>
+  <si>
+    <t>Verify that the search results list contains "Playwright"</t>
+  </si>
+  <si>
+    <t>Results mention the query</t>
+  </si>
+  <si>
+    <t>Verify that the page title contains "Playwright automation"</t>
+  </si>
+  <si>
+    <t>Tab shows the query</t>
+  </si>
+  <si>
+    <t>TC-YT-006</t>
+  </si>
+  <si>
+    <t>Open a video and verify its details</t>
+  </si>
+  <si>
+    <t>Verify that the video title contains "Playwright"</t>
+  </si>
+  <si>
+    <t>The heading names the video</t>
+  </si>
+  <si>
+    <t>TC-YT-007</t>
+  </si>
+  <si>
+    <t>Return to the homepage using the logo</t>
+  </si>
+  <si>
+    <t>Search results are displayed</t>
+  </si>
+  <si>
+    <t>Click the YouTube logo</t>
+  </si>
+  <si>
+    <t>The browser returns to the homepage</t>
+  </si>
+  <si>
+    <t>Tab reads YouTube</t>
   </si>
 </sst>
 </file>
@@ -511,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -946,6 +994,346 @@
         <v>39</v>
       </c>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="77">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -179,6 +179,69 @@
   </si>
   <si>
     <t>Tab reads YouTube</t>
+  </si>
+  <si>
+    <t>TC-YT-008</t>
+  </si>
+  <si>
+    <t>Search results mention a named alternative</t>
+  </si>
+  <si>
+    <t>Enter "Playwright vs Selenium" in the search box</t>
+  </si>
+  <si>
+    <t>Verify that the search results list contains "Selenium"</t>
+  </si>
+  <si>
+    <t>A result names Selenium</t>
+  </si>
+  <si>
+    <t>TC-YT-009</t>
+  </si>
+  <si>
+    <t>Going back from a video restores the results list</t>
+  </si>
+  <si>
+    <t>The results list is shown again</t>
+  </si>
+  <si>
+    <t>TC-YT-010</t>
+  </si>
+  <si>
+    <t>The homepage shows no video player</t>
+  </si>
+  <si>
+    <t>Verify that the video player is not visible</t>
+  </si>
+  <si>
+    <t>No player is rendered on the homepage</t>
+  </si>
+  <si>
+    <t>TC-YT-011</t>
+  </si>
+  <si>
+    <t>Refine a search from the results page</t>
+  </si>
+  <si>
+    <t>The query is replaced</t>
+  </si>
+  <si>
+    <t>The new search is submitted</t>
+  </si>
+  <si>
+    <t>Verify that the page title contains "Playwright vs Selenium"</t>
+  </si>
+  <si>
+    <t>Tab shows the new query</t>
+  </si>
+  <si>
+    <t>TC-YT-012</t>
+  </si>
+  <si>
+    <t>Open a video then return to the homepage</t>
+  </si>
+  <si>
+    <t>The player is gone</t>
   </si>
 </sst>
 </file>
@@ -559,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1334,6 +1397,516 @@
         <v>25</v>
       </c>
     </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>66</v>
+      </c>
+      <c r="E60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>72</v>
+      </c>
+      <c r="E67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>66</v>
+      </c>
+      <c r="E75" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="600" windowWidth="19815" windowHeight="7110"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ManualTestCases" state="visible" r:id="rId4"/>
+    <sheet name="ManualTestCases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="155">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -242,22 +245,258 @@
   </si>
   <si>
     <t>The player is gone</t>
+  </si>
+  <si>
+    <t>TC-YT-013</t>
+  </si>
+  <si>
+    <t>Search for a video</t>
+  </si>
+  <si>
+    <t>Open YouTube, enter a search term, submit</t>
+  </si>
+  <si>
+    <t>Relevant search results appear</t>
+  </si>
+  <si>
+    <t>TC-YT-014</t>
+  </si>
+  <si>
+    <t>Search with no results</t>
+  </si>
+  <si>
+    <t>Search for a unique, unlikely phrase</t>
+  </si>
+  <si>
+    <t>No-results message or empty results are shown</t>
+  </si>
+  <si>
+    <t>TC-YT-015</t>
+  </si>
+  <si>
+    <t>Clear search text</t>
+  </si>
+  <si>
+    <t>Enter a query, clear the search field</t>
+  </si>
+  <si>
+    <t>Search field becomes empty</t>
+  </si>
+  <si>
+    <t>TC-YT-016</t>
+  </si>
+  <si>
+    <t>Search using Enter</t>
+  </si>
+  <si>
+    <t>Enter a query and press Enter</t>
+  </si>
+  <si>
+    <t>Search results appear</t>
+  </si>
+  <si>
+    <t>TC-YT-017</t>
+  </si>
+  <si>
+    <t>Search using the search button</t>
+  </si>
+  <si>
+    <t>Enter a query and click Search</t>
+  </si>
+  <si>
+    <t>TC-YT-018</t>
+  </si>
+  <si>
+    <t>Open a video</t>
+  </si>
+  <si>
+    <t>Search for a video and select a result</t>
+  </si>
+  <si>
+    <t>Video watch page opens</t>
+  </si>
+  <si>
+    <t>TC-YT-019</t>
+  </si>
+  <si>
+    <t>Verify video title</t>
+  </si>
+  <si>
+    <t>The title is visible on the watch page</t>
+  </si>
+  <si>
+    <t>TC-YT-020</t>
+  </si>
+  <si>
+    <t>Play and pause a video</t>
+  </si>
+  <si>
+    <t>Open a playable video, click Play, then Pause</t>
+  </si>
+  <si>
+    <t>Playback starts and pauses</t>
+  </si>
+  <si>
+    <t>TC-YT-021</t>
+  </si>
+  <si>
+    <t>Adjust volume</t>
+  </si>
+  <si>
+    <t>Open a video and change the volume</t>
+  </si>
+  <si>
+    <t>Volume level changes</t>
+  </si>
+  <si>
+    <t>TC-YT-022</t>
+  </si>
+  <si>
+    <t>Toggle mute</t>
+  </si>
+  <si>
+    <t>Click the mute control twice</t>
+  </si>
+  <si>
+    <t>Audio mutes and unmutes</t>
+  </si>
+  <si>
+    <t>TC-YT-023</t>
+  </si>
+  <si>
+    <t>Toggle full screen</t>
+  </si>
+  <si>
+    <t>Enter and exit full-screen mode</t>
+  </si>
+  <si>
+    <t>Video player changes display mode</t>
+  </si>
+  <si>
+    <t>TC-YT-024</t>
+  </si>
+  <si>
+    <t>Expand video description</t>
+  </si>
+  <si>
+    <t>Open a video and expand its description</t>
+  </si>
+  <si>
+    <t>More description text is displayed</t>
+  </si>
+  <si>
+    <t>TC-YT-025</t>
+  </si>
+  <si>
+    <t>Open channel from a video</t>
+  </si>
+  <si>
+    <t>Click the creator's channel name</t>
+  </si>
+  <si>
+    <t>Channel page opens</t>
+  </si>
+  <si>
+    <t>TC-YT-026</t>
+  </si>
+  <si>
+    <t>Open the Comments section</t>
+  </si>
+  <si>
+    <t>Scroll to comments on a video</t>
+  </si>
+  <si>
+    <t>Comments section is displayed, when available</t>
+  </si>
+  <si>
+    <t>TC-YT-027</t>
+  </si>
+  <si>
+    <t>Like a video</t>
+  </si>
+  <si>
+    <t>Click Like while signed in</t>
+  </si>
+  <si>
+    <t>Like state is updated</t>
+  </si>
+  <si>
+    <t>TC-YT-028</t>
+  </si>
+  <si>
+    <t>Subscribe to a channel</t>
+  </si>
+  <si>
+    <t>Click Subscribe while signed in</t>
+  </si>
+  <si>
+    <t>Subscription state is updated</t>
+  </si>
+  <si>
+    <t>TC-YT-029</t>
+  </si>
+  <si>
+    <t>Open the YouTube homepage</t>
+  </si>
+  <si>
+    <t>Navigate to the homepage</t>
+  </si>
+  <si>
+    <t>Homepage loads</t>
+  </si>
+  <si>
+    <t>TC-YT-030</t>
+  </si>
+  <si>
+    <t>Open a video from search results in a new tab</t>
+  </si>
+  <si>
+    <t>Open a result in a new tab</t>
+  </si>
+  <si>
+    <t>The new tab displays the selected video</t>
+  </si>
+  <si>
+    <t>TC-YT-031</t>
+  </si>
+  <si>
+    <t>Browser Back navigation</t>
+  </si>
+  <si>
+    <t>Open a video from search, then go Back</t>
+  </si>
+  <si>
+    <t>Previous search results return</t>
+  </si>
+  <si>
+    <t>TC-YT-032</t>
+  </si>
+  <si>
+    <t>Browser Forward navigation</t>
+  </si>
+  <si>
+    <t>Go Back, then Forward</t>
+  </si>
+  <si>
+    <t>The video watch page returns</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -280,9 +519,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,9 +863,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E95"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -632,7 +874,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -666,7 +908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -683,7 +925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -700,7 +942,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -717,7 +959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -734,7 +976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -751,7 +993,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -768,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -785,7 +1027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -802,7 +1044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -819,7 +1061,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -836,7 +1078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -853,7 +1095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -870,7 +1112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -887,7 +1129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -904,7 +1146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -921,7 +1163,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -938,7 +1180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -955,7 +1197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -972,7 +1214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -989,7 +1231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1006,7 +1248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1023,7 +1265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1040,7 +1282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1057,7 +1299,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1074,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1091,7 +1333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1108,7 +1350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1125,7 +1367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1142,7 +1384,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1159,7 +1401,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1176,7 +1418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1193,7 +1435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -1210,7 +1452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -1227,7 +1469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -1244,7 +1486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -1261,7 +1503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -1278,7 +1520,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -1295,7 +1537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -1312,7 +1554,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -1329,7 +1571,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -1346,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1363,7 +1605,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -1380,7 +1622,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1397,7 +1639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -1414,7 +1656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -1431,7 +1673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -1448,7 +1690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1465,7 +1707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1482,7 +1724,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -1499,7 +1741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -1516,7 +1758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -1533,7 +1775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1550,7 +1792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -1567,7 +1809,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1584,7 +1826,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -1601,7 +1843,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -1618,7 +1860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1635,7 +1877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -1652,7 +1894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -1669,7 +1911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -1686,7 +1928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1703,7 +1945,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -1720,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1737,7 +1979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -1754,7 +1996,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1771,7 +2013,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -1788,7 +2030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -1805,7 +2047,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -1822,7 +2064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1839,7 +2081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -1856,7 +2098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1873,7 +2115,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -1890,7 +2132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -1907,8 +2149,348 @@
         <v>76</v>
       </c>
     </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="30">
+      <c r="A77" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C87" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="30">
+      <c r="A89" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="30">
+      <c r="A93" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -1,20 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="600" windowWidth="19815" windowHeight="7110"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="ManualTestCases" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="ManualTestCases" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="173">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -253,22 +250,28 @@
     <t>Search for a video</t>
   </si>
   <si>
-    <t>Open YouTube, enter a search term, submit</t>
-  </si>
-  <si>
-    <t>Relevant search results appear</t>
-  </si>
-  <si>
     <t>TC-YT-014</t>
   </si>
   <si>
     <t>Search with no results</t>
   </si>
   <si>
-    <t>Search for a unique, unlikely phrase</t>
-  </si>
-  <si>
-    <t>No-results message or empty results are shown</t>
+    <t>Enter "zzqqxx no such video" in the search box</t>
+  </si>
+  <si>
+    <t>The unlikely phrase is entered</t>
+  </si>
+  <si>
+    <t>Verify that the no results message is visible</t>
+  </si>
+  <si>
+    <t>The empty state is shown</t>
+  </si>
+  <si>
+    <t>Verify that the first search result is not visible</t>
+  </si>
+  <si>
+    <t>No videos are listed</t>
   </si>
   <si>
     <t>TC-YT-015</t>
@@ -277,10 +280,13 @@
     <t>Clear search text</t>
   </si>
   <si>
-    <t>Enter a query, clear the search field</t>
-  </si>
-  <si>
-    <t>Search field becomes empty</t>
+    <t>Clear the search box</t>
+  </si>
+  <si>
+    <t>The field is emptied</t>
+  </si>
+  <si>
+    <t>The field is still there, now empty</t>
   </si>
   <si>
     <t>TC-YT-016</t>
@@ -289,10 +295,7 @@
     <t>Search using Enter</t>
   </si>
   <si>
-    <t>Enter a query and press Enter</t>
-  </si>
-  <si>
-    <t>Search results appear</t>
+    <t>The results page is shown</t>
   </si>
   <si>
     <t>TC-YT-017</t>
@@ -301,40 +304,43 @@
     <t>Search using the search button</t>
   </si>
   <si>
-    <t>Enter a query and click Search</t>
-  </si>
-  <si>
     <t>TC-YT-018</t>
   </si>
   <si>
     <t>Open a video</t>
   </si>
   <si>
-    <t>Search for a video and select a result</t>
-  </si>
-  <si>
-    <t>Video watch page opens</t>
-  </si>
-  <si>
     <t>TC-YT-019</t>
   </si>
   <si>
     <t>Verify video title</t>
   </si>
   <si>
-    <t>The title is visible on the watch page</t>
-  </si>
-  <si>
     <t>TC-YT-020</t>
   </si>
   <si>
     <t>Play and pause a video</t>
   </si>
   <si>
-    <t>Open a playable video, click Play, then Pause</t>
-  </si>
-  <si>
-    <t>Playback starts and pauses</t>
+    <t>Click the Play button</t>
+  </si>
+  <si>
+    <t>Playback starts</t>
+  </si>
+  <si>
+    <t>Verify that the Play button contains "Pause"</t>
+  </si>
+  <si>
+    <t>The control now offers Pause</t>
+  </si>
+  <si>
+    <t>Playback stops</t>
+  </si>
+  <si>
+    <t>Verify that the Play button contains "Play"</t>
+  </si>
+  <si>
+    <t>The control offers Play again</t>
   </si>
   <si>
     <t>TC-YT-021</t>
@@ -343,10 +349,16 @@
     <t>Adjust volume</t>
   </si>
   <si>
-    <t>Open a video and change the volume</t>
-  </si>
-  <si>
-    <t>Volume level changes</t>
+    <t>Verify that the volume slider is visible</t>
+  </si>
+  <si>
+    <t>The volume control is shown</t>
+  </si>
+  <si>
+    <t>Enter "40" in the volume slider</t>
+  </si>
+  <si>
+    <t>The volume is lowered</t>
   </si>
   <si>
     <t>TC-YT-022</t>
@@ -355,10 +367,25 @@
     <t>Toggle mute</t>
   </si>
   <si>
-    <t>Click the mute control twice</t>
-  </si>
-  <si>
-    <t>Audio mutes and unmutes</t>
+    <t>Click the Mute button</t>
+  </si>
+  <si>
+    <t>Audio is muted</t>
+  </si>
+  <si>
+    <t>Verify that the Mute button contains "Unmute"</t>
+  </si>
+  <si>
+    <t>The control now offers Unmute</t>
+  </si>
+  <si>
+    <t>Audio is restored</t>
+  </si>
+  <si>
+    <t>Verify that the Mute button contains "Mute"</t>
+  </si>
+  <si>
+    <t>The control offers Mute again</t>
   </si>
   <si>
     <t>TC-YT-023</t>
@@ -367,10 +394,13 @@
     <t>Toggle full screen</t>
   </si>
   <si>
-    <t>Enter and exit full-screen mode</t>
-  </si>
-  <si>
-    <t>Video player changes display mode</t>
+    <t>Click the Full screen button</t>
+  </si>
+  <si>
+    <t>The player fills the window</t>
+  </si>
+  <si>
+    <t>The player is still rendered</t>
   </si>
   <si>
     <t>TC-YT-024</t>
@@ -379,10 +409,22 @@
     <t>Expand video description</t>
   </si>
   <si>
-    <t>Open a video and expand its description</t>
-  </si>
-  <si>
-    <t>More description text is displayed</t>
+    <t>Verify that the expanded description is not visible</t>
+  </si>
+  <si>
+    <t>The description starts collapsed</t>
+  </si>
+  <si>
+    <t>Click the Show more button</t>
+  </si>
+  <si>
+    <t>The description expands</t>
+  </si>
+  <si>
+    <t>Verify that the expanded description is visible</t>
+  </si>
+  <si>
+    <t>The rest of the description is shown</t>
   </si>
   <si>
     <t>TC-YT-025</t>
@@ -391,10 +433,22 @@
     <t>Open channel from a video</t>
   </si>
   <si>
-    <t>Click the creator's channel name</t>
-  </si>
-  <si>
-    <t>Channel page opens</t>
+    <t>Click the channel name link</t>
+  </si>
+  <si>
+    <t>The channel page opens</t>
+  </si>
+  <si>
+    <t>Verify that the URL contains "/channel"</t>
+  </si>
+  <si>
+    <t>The channel page is shown</t>
+  </si>
+  <si>
+    <t>Verify that the channel page heading is visible</t>
+  </si>
+  <si>
+    <t>The channel is named</t>
   </si>
   <si>
     <t>TC-YT-026</t>
@@ -403,34 +457,52 @@
     <t>Open the Comments section</t>
   </si>
   <si>
-    <t>Scroll to comments on a video</t>
-  </si>
-  <si>
-    <t>Comments section is displayed, when available</t>
+    <t>Verify that the Comments section is visible</t>
+  </si>
+  <si>
+    <t>Comments are shown</t>
   </si>
   <si>
     <t>TC-YT-027</t>
   </si>
   <si>
-    <t>Like a video</t>
-  </si>
-  <si>
-    <t>Click Like while signed in</t>
-  </si>
-  <si>
-    <t>Like state is updated</t>
+    <t>Liking a video while signed out asks for sign-in</t>
+  </si>
+  <si>
+    <t>User has internet access. User is not signed in.</t>
+  </si>
+  <si>
+    <t>Verify that the sign-in prompt is not visible</t>
+  </si>
+  <si>
+    <t>Nothing is asked yet</t>
+  </si>
+  <si>
+    <t>Click the Like button</t>
+  </si>
+  <si>
+    <t>Sign-in is requested</t>
+  </si>
+  <si>
+    <t>Verify that the sign-in prompt is visible</t>
+  </si>
+  <si>
+    <t>The viewer is asked to sign in</t>
   </si>
   <si>
     <t>TC-YT-028</t>
   </si>
   <si>
-    <t>Subscribe to a channel</t>
-  </si>
-  <si>
-    <t>Click Subscribe while signed in</t>
-  </si>
-  <si>
-    <t>Subscription state is updated</t>
+    <t>Subscribing while signed out asks for sign-in</t>
+  </si>
+  <si>
+    <t>Verify that the Subscribe button is visible</t>
+  </si>
+  <si>
+    <t>Subscribing is offered</t>
+  </si>
+  <si>
+    <t>Click the Subscribe button</t>
   </si>
   <si>
     <t>TC-YT-029</t>
@@ -439,34 +511,13 @@
     <t>Open the YouTube homepage</t>
   </si>
   <si>
-    <t>Navigate to the homepage</t>
-  </si>
-  <si>
-    <t>Homepage loads</t>
-  </si>
-  <si>
-    <t>TC-YT-030</t>
-  </si>
-  <si>
-    <t>Open a video from search results in a new tab</t>
-  </si>
-  <si>
-    <t>Open a result in a new tab</t>
-  </si>
-  <si>
-    <t>The new tab displays the selected video</t>
-  </si>
-  <si>
     <t>TC-YT-031</t>
   </si>
   <si>
     <t>Browser Back navigation</t>
   </si>
   <si>
-    <t>Open a video from search, then go Back</t>
-  </si>
-  <si>
-    <t>Previous search results return</t>
+    <t>The results page is shown again</t>
   </si>
   <si>
     <t>TC-YT-032</t>
@@ -475,28 +526,26 @@
     <t>Browser Forward navigation</t>
   </si>
   <si>
-    <t>Go Back, then Forward</t>
-  </si>
-  <si>
-    <t>The video watch page returns</t>
+    <t>Navigate forward</t>
+  </si>
+  <si>
+    <t>The browser returns to the video</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -519,12 +568,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,9 +909,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E95"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E188"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -874,7 +920,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,7 +937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -908,7 +954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -925,7 +971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -942,7 +988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -959,7 +1005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -976,7 +1022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -993,7 +1039,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1010,7 +1056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1027,7 +1073,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1044,7 +1090,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1061,7 +1107,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1078,7 +1124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1095,7 +1141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1112,7 +1158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1129,7 +1175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1146,7 +1192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1163,7 +1209,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1180,7 +1226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1197,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1214,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1231,7 +1277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1248,7 +1294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1265,7 +1311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1282,7 +1328,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1316,7 +1362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1333,7 +1379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1350,7 +1396,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1367,7 +1413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1384,7 +1430,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1401,7 +1447,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1418,7 +1464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1435,7 +1481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -1452,7 +1498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -1469,7 +1515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -1486,7 +1532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -1503,7 +1549,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -1520,7 +1566,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -1537,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -1554,7 +1600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -1571,7 +1617,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -1588,7 +1634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1605,7 +1651,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -1622,7 +1668,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1639,7 +1685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -1656,7 +1702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -1673,7 +1719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -1690,7 +1736,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1707,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1724,7 +1770,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -1741,7 +1787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -1758,7 +1804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -1775,7 +1821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1792,7 +1838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -1809,7 +1855,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1826,7 +1872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -1843,7 +1889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -1860,7 +1906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1877,7 +1923,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -1894,7 +1940,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -1911,7 +1957,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -1928,7 +1974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1945,7 +1991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -1962,7 +2008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1979,7 +2025,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -1996,7 +2042,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -2013,7 +2059,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -2030,7 +2076,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -2047,7 +2093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -2064,7 +2110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2081,7 +2127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -2098,7 +2144,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -2115,7 +2161,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -2132,7 +2178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -2149,348 +2195,1929 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" t="s">
         <v>78</v>
       </c>
       <c r="C76" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>79</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="B80" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="30">
-      <c r="A77" s="2" t="s">
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="E81" t="s">
         <v>82</v>
       </c>
-      <c r="C77" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="2" t="s">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" t="s">
+        <v>80</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>79</v>
+      </c>
+      <c r="B83" t="s">
+        <v>80</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
         <v>83</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E83" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="E84" t="s">
         <v>86</v>
       </c>
-      <c r="C78" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="2" t="s">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>87</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="B85" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="2" t="s">
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" t="s">
         <v>89</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="E87" t="s">
         <v>90</v>
       </c>
-      <c r="C79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="2" t="s">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" t="s">
         <v>91</v>
       </c>
-      <c r="E79" s="2" t="s">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="2" t="s">
+      <c r="B89" t="s">
         <v>93</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" t="s">
+        <v>93</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" t="s">
+        <v>38</v>
+      </c>
+      <c r="E92" t="s">
         <v>94</v>
       </c>
-      <c r="C80" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="2" t="s">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>93</v>
+      </c>
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>95</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2" t="s">
+      <c r="B94" t="s">
         <v>96</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C96" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>96</v>
+      </c>
+      <c r="C97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>97</v>
       </c>
-      <c r="C81" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="2" t="s">
+      <c r="B98" t="s">
         <v>98</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" t="s">
+        <v>98</v>
+      </c>
+      <c r="C100" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>97</v>
+      </c>
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>97</v>
+      </c>
+      <c r="B102" t="s">
+        <v>98</v>
+      </c>
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" t="s">
+        <v>98</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2" t="s">
+      <c r="B104" t="s">
         <v>100</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>99</v>
+      </c>
+      <c r="B105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>99</v>
+      </c>
+      <c r="B106" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>99</v>
+      </c>
+      <c r="B107" t="s">
+        <v>100</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>99</v>
+      </c>
+      <c r="B108" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" t="s">
+        <v>48</v>
+      </c>
+      <c r="E108" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>101</v>
       </c>
-      <c r="C82" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E82" s="2" t="s">
+      <c r="B109" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2" t="s">
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>101</v>
+      </c>
+      <c r="B110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>101</v>
+      </c>
+      <c r="B111" t="s">
+        <v>102</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>101</v>
+      </c>
+      <c r="B112" t="s">
+        <v>102</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>101</v>
+      </c>
+      <c r="B113" t="s">
+        <v>102</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="E113" t="s">
         <v>104</v>
       </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="2" t="s">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>101</v>
+      </c>
+      <c r="B114" t="s">
+        <v>102</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
         <v>105</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E114" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="2" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>101</v>
+      </c>
+      <c r="B115" t="s">
+        <v>102</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>103</v>
+      </c>
+      <c r="E115" t="s">
         <v>107</v>
       </c>
-      <c r="B84" s="2" t="s">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>101</v>
+      </c>
+      <c r="B116" t="s">
+        <v>102</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" t="s">
         <v>108</v>
       </c>
-      <c r="C84" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="2" t="s">
+      <c r="E116" t="s">
         <v>109</v>
       </c>
-      <c r="E84" s="2" t="s">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2" t="s">
+      <c r="B117" t="s">
         <v>111</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>8</v>
+      </c>
+      <c r="E117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>110</v>
+      </c>
+      <c r="B118" t="s">
+        <v>111</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>110</v>
+      </c>
+      <c r="B119" t="s">
+        <v>111</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>110</v>
+      </c>
+      <c r="B120" t="s">
+        <v>111</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>110</v>
+      </c>
+      <c r="B121" t="s">
+        <v>111</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" t="s">
         <v>112</v>
       </c>
-      <c r="C85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="2" t="s">
+      <c r="E121" t="s">
         <v>113</v>
       </c>
-      <c r="E85" s="2" t="s">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>110</v>
+      </c>
+      <c r="B122" t="s">
+        <v>111</v>
+      </c>
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="2" t="s">
+      <c r="E122" t="s">
         <v>115</v>
       </c>
-      <c r="B86" s="2" t="s">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>116</v>
       </c>
-      <c r="C86" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="B123" t="s">
         <v>117</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>116</v>
+      </c>
+      <c r="B124" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+      <c r="B125" t="s">
+        <v>117</v>
+      </c>
+      <c r="C125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>116</v>
+      </c>
+      <c r="B126" t="s">
+        <v>117</v>
+      </c>
+      <c r="C126" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>116</v>
+      </c>
+      <c r="B127" t="s">
+        <v>117</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="2" t="s">
+      <c r="E127" t="s">
         <v>119</v>
       </c>
-      <c r="B87" s="2" t="s">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>116</v>
+      </c>
+      <c r="B128" t="s">
+        <v>117</v>
+      </c>
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" t="s">
         <v>120</v>
       </c>
-      <c r="C87" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="2" t="s">
+      <c r="E128" t="s">
         <v>121</v>
       </c>
-      <c r="E87" s="2" t="s">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>116</v>
+      </c>
+      <c r="B129" t="s">
+        <v>117</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>118</v>
+      </c>
+      <c r="E129" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="2" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
         <v>123</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="E130" t="s">
         <v>124</v>
       </c>
-      <c r="C88" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="2" t="s">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>125</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="B131" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="30">
-      <c r="A89" s="2" t="s">
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>125</v>
+      </c>
+      <c r="B132" t="s">
+        <v>126</v>
+      </c>
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>125</v>
+      </c>
+      <c r="B133" t="s">
+        <v>126</v>
+      </c>
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>125</v>
+      </c>
+      <c r="B134" t="s">
+        <v>126</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>125</v>
+      </c>
+      <c r="B135" t="s">
+        <v>126</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" t="s">
         <v>127</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="E135" t="s">
         <v>128</v>
       </c>
-      <c r="C89" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="2" t="s">
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>125</v>
+      </c>
+      <c r="B136" t="s">
+        <v>126</v>
+      </c>
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" t="s">
+        <v>32</v>
+      </c>
+      <c r="E136" t="s">
         <v>129</v>
       </c>
-      <c r="E89" s="2" t="s">
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="2" t="s">
+      <c r="B137" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138" t="s">
+        <v>131</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>130</v>
+      </c>
+      <c r="B139" t="s">
+        <v>131</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>130</v>
+      </c>
+      <c r="B140" t="s">
+        <v>131</v>
+      </c>
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>130</v>
+      </c>
+      <c r="B141" t="s">
+        <v>131</v>
+      </c>
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" t="s">
         <v>132</v>
       </c>
-      <c r="C90" t="s">
-        <v>7</v>
-      </c>
-      <c r="D90" s="2" t="s">
+      <c r="E141" t="s">
         <v>133</v>
       </c>
-      <c r="E90" s="2" t="s">
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>130</v>
+      </c>
+      <c r="B142" t="s">
+        <v>131</v>
+      </c>
+      <c r="C142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="2" t="s">
+      <c r="E142" t="s">
         <v>135</v>
       </c>
-      <c r="B91" s="2" t="s">
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>130</v>
+      </c>
+      <c r="B143" t="s">
+        <v>131</v>
+      </c>
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" t="s">
         <v>136</v>
       </c>
-      <c r="C91" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="2" t="s">
+      <c r="E143" t="s">
         <v>137</v>
       </c>
-      <c r="E91" s="2" t="s">
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="2" t="s">
+      <c r="B144" t="s">
         <v>139</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>138</v>
+      </c>
+      <c r="B145" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>138</v>
+      </c>
+      <c r="B146" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" t="s">
+        <v>31</v>
+      </c>
+      <c r="E146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>138</v>
+      </c>
+      <c r="B147" t="s">
+        <v>139</v>
+      </c>
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>138</v>
+      </c>
+      <c r="B148" t="s">
+        <v>139</v>
+      </c>
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" t="s">
         <v>140</v>
       </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" s="2" t="s">
+      <c r="E148" t="s">
         <v>141</v>
       </c>
-      <c r="E92" s="2" t="s">
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>138</v>
+      </c>
+      <c r="B149" t="s">
+        <v>139</v>
+      </c>
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" ht="30">
-      <c r="A93" s="2" t="s">
+      <c r="E149" t="s">
         <v>143</v>
       </c>
-      <c r="B93" s="2" t="s">
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>138</v>
+      </c>
+      <c r="B150" t="s">
+        <v>139</v>
+      </c>
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" t="s">
         <v>144</v>
       </c>
-      <c r="C93" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="2" t="s">
+      <c r="E150" t="s">
         <v>145</v>
       </c>
-      <c r="E93" s="2" t="s">
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="2" t="s">
+      <c r="B151" t="s">
         <v>147</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>146</v>
+      </c>
+      <c r="B152" t="s">
+        <v>147</v>
+      </c>
+      <c r="C152" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>146</v>
+      </c>
+      <c r="B153" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" t="s">
+        <v>31</v>
+      </c>
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>146</v>
+      </c>
+      <c r="B154" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>146</v>
+      </c>
+      <c r="B155" t="s">
+        <v>147</v>
+      </c>
+      <c r="C155" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" t="s">
         <v>148</v>
       </c>
-      <c r="C94" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="2" t="s">
+      <c r="E155" t="s">
         <v>149</v>
       </c>
-      <c r="E94" s="2" t="s">
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="2" t="s">
+      <c r="B156" t="s">
         <v>151</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C156" t="s">
         <v>152</v>
       </c>
-      <c r="C95" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="D156" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>150</v>
+      </c>
+      <c r="B157" t="s">
+        <v>151</v>
+      </c>
+      <c r="C157" t="s">
+        <v>152</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>150</v>
+      </c>
+      <c r="B158" t="s">
+        <v>151</v>
+      </c>
+      <c r="C158" t="s">
+        <v>152</v>
+      </c>
+      <c r="D158" t="s">
+        <v>31</v>
+      </c>
+      <c r="E158" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>150</v>
+      </c>
+      <c r="B159" t="s">
+        <v>151</v>
+      </c>
+      <c r="C159" t="s">
+        <v>152</v>
+      </c>
+      <c r="D159" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>150</v>
+      </c>
+      <c r="B160" t="s">
+        <v>151</v>
+      </c>
+      <c r="C160" t="s">
+        <v>152</v>
+      </c>
+      <c r="D160" t="s">
         <v>153</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E160" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>150</v>
+      </c>
+      <c r="B161" t="s">
+        <v>151</v>
+      </c>
+      <c r="C161" t="s">
+        <v>152</v>
+      </c>
+      <c r="D161" t="s">
+        <v>155</v>
+      </c>
+      <c r="E161" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>150</v>
+      </c>
+      <c r="B162" t="s">
+        <v>151</v>
+      </c>
+      <c r="C162" t="s">
+        <v>152</v>
+      </c>
+      <c r="D162" t="s">
+        <v>157</v>
+      </c>
+      <c r="E162" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>159</v>
+      </c>
+      <c r="B163" t="s">
+        <v>160</v>
+      </c>
+      <c r="C163" t="s">
+        <v>152</v>
+      </c>
+      <c r="D163" t="s">
+        <v>8</v>
+      </c>
+      <c r="E163" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>159</v>
+      </c>
+      <c r="B164" t="s">
+        <v>160</v>
+      </c>
+      <c r="C164" t="s">
+        <v>152</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>159</v>
+      </c>
+      <c r="B165" t="s">
+        <v>160</v>
+      </c>
+      <c r="C165" t="s">
+        <v>152</v>
+      </c>
+      <c r="D165" t="s">
+        <v>31</v>
+      </c>
+      <c r="E165" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>159</v>
+      </c>
+      <c r="B166" t="s">
+        <v>160</v>
+      </c>
+      <c r="C166" t="s">
+        <v>152</v>
+      </c>
+      <c r="D166" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>159</v>
+      </c>
+      <c r="B167" t="s">
+        <v>160</v>
+      </c>
+      <c r="C167" t="s">
+        <v>152</v>
+      </c>
+      <c r="D167" t="s">
+        <v>161</v>
+      </c>
+      <c r="E167" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>159</v>
+      </c>
+      <c r="B168" t="s">
+        <v>160</v>
+      </c>
+      <c r="C168" t="s">
+        <v>152</v>
+      </c>
+      <c r="D168" t="s">
+        <v>163</v>
+      </c>
+      <c r="E168" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>159</v>
+      </c>
+      <c r="B169" t="s">
+        <v>160</v>
+      </c>
+      <c r="C169" t="s">
+        <v>152</v>
+      </c>
+      <c r="D169" t="s">
+        <v>157</v>
+      </c>
+      <c r="E169" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>164</v>
+      </c>
+      <c r="B170" t="s">
+        <v>165</v>
+      </c>
+      <c r="C170" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>164</v>
+      </c>
+      <c r="B171" t="s">
+        <v>165</v>
+      </c>
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" t="s">
+        <v>26</v>
+      </c>
+      <c r="E171" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>164</v>
+      </c>
+      <c r="B172" t="s">
+        <v>165</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>164</v>
+      </c>
+      <c r="B173" t="s">
+        <v>165</v>
+      </c>
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" t="s">
+        <v>24</v>
+      </c>
+      <c r="E173" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>166</v>
+      </c>
+      <c r="B174" t="s">
+        <v>167</v>
+      </c>
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>166</v>
+      </c>
+      <c r="B175" t="s">
+        <v>167</v>
+      </c>
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>166</v>
+      </c>
+      <c r="B176" t="s">
+        <v>167</v>
+      </c>
+      <c r="C176" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176" t="s">
+        <v>31</v>
+      </c>
+      <c r="E176" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>166</v>
+      </c>
+      <c r="B177" t="s">
+        <v>167</v>
+      </c>
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>166</v>
+      </c>
+      <c r="B178" t="s">
+        <v>167</v>
+      </c>
+      <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>166</v>
+      </c>
+      <c r="B179" t="s">
+        <v>167</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>36</v>
+      </c>
+      <c r="E179" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>166</v>
+      </c>
+      <c r="B180" t="s">
+        <v>167</v>
+      </c>
+      <c r="C180" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" t="s">
+        <v>38</v>
+      </c>
+      <c r="E180" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>169</v>
+      </c>
+      <c r="B181" t="s">
+        <v>170</v>
+      </c>
+      <c r="C181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>169</v>
+      </c>
+      <c r="B182" t="s">
+        <v>170</v>
+      </c>
+      <c r="C182" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>169</v>
+      </c>
+      <c r="B183" t="s">
+        <v>170</v>
+      </c>
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" t="s">
+        <v>31</v>
+      </c>
+      <c r="E183" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>169</v>
+      </c>
+      <c r="B184" t="s">
+        <v>170</v>
+      </c>
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>169</v>
+      </c>
+      <c r="B185" t="s">
+        <v>170</v>
+      </c>
+      <c r="C185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" t="s">
+        <v>36</v>
+      </c>
+      <c r="E185" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>169</v>
+      </c>
+      <c r="B186" t="s">
+        <v>170</v>
+      </c>
+      <c r="C186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" t="s">
+        <v>38</v>
+      </c>
+      <c r="E186" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>169</v>
+      </c>
+      <c r="B187" t="s">
+        <v>170</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" t="s">
+        <v>171</v>
+      </c>
+      <c r="E187" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>169</v>
+      </c>
+      <c r="B188" t="s">
+        <v>170</v>
+      </c>
+      <c r="C188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="175">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>YouTube homepage is displayed</t>
+  </si>
+  <si>
+    <t>Close the cookie consent dialog if it is displayed</t>
+  </si>
+  <si>
+    <t>The page is not covered by the consent dialog</t>
   </si>
   <si>
     <t>Enter "Playwright automation" in the search box</t>
@@ -910,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1041,1642 +1047,1642 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
         <v>34</v>
       </c>
-      <c r="B20" t="s">
+      <c r="E20" t="s">
         <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
         <v>40</v>
       </c>
-      <c r="B29" t="s">
+      <c r="E29" t="s">
         <v>41</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
         <v>46</v>
       </c>
-      <c r="B36" t="s">
+      <c r="E36" t="s">
         <v>47</v>
-      </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
         <v>50</v>
       </c>
-      <c r="B44" t="s">
+      <c r="E44" t="s">
         <v>51</v>
-      </c>
-      <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" t="s">
         <v>56</v>
-      </c>
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C57" t="s">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
         <v>7</v>
       </c>
       <c r="D58" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" t="s">
         <v>64</v>
       </c>
-      <c r="B59" t="s">
-        <v>65</v>
-      </c>
       <c r="C59" t="s">
         <v>7</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" t="s">
         <v>64</v>
       </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
       <c r="C60" t="s">
         <v>7</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
       </c>
       <c r="D63" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
         <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E66" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
         <v>7</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C70" t="s">
         <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
         <v>7</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
         <v>7</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
         <v>7</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C75" t="s">
         <v>7</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C76" t="s">
         <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
         <v>7</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
       </c>
       <c r="D78" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" t="s">
         <v>77</v>
       </c>
-      <c r="B79" t="s">
-        <v>78</v>
-      </c>
       <c r="C79" t="s">
         <v>7</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C80" t="s">
         <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C81" t="s">
         <v>7</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E81" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C82" t="s">
         <v>7</v>
       </c>
       <c r="D82" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C83" t="s">
         <v>7</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
         <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E85" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C86" t="s">
         <v>7</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C87" t="s">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E87" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C88" t="s">
         <v>7</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C89" t="s">
         <v>7</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C92" t="s">
         <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E92" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C93" t="s">
         <v>7</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
         <v>7</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
         <v>7</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
         <v>7</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
         <v>7</v>
       </c>
       <c r="D97" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E97" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C98" t="s">
         <v>7</v>
       </c>
       <c r="D98" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E98" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C99" t="s">
         <v>7</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C100" t="s">
         <v>7</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C101" t="s">
         <v>7</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C102" t="s">
         <v>7</v>
       </c>
       <c r="D102" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C103" t="s">
         <v>7</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E103" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C104" t="s">
         <v>7</v>
@@ -2690,10 +2696,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C105" t="s">
         <v>7</v>
@@ -2707,16 +2713,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C106" t="s">
         <v>7</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E106" t="s">
         <v>13</v>
@@ -2724,520 +2730,520 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C107" t="s">
         <v>7</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C108" t="s">
         <v>7</v>
       </c>
       <c r="D108" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E108" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C109" t="s">
         <v>7</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E109" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C110" t="s">
         <v>7</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E110" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C111" t="s">
         <v>7</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B112" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C112" t="s">
         <v>7</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
         <v>7</v>
       </c>
       <c r="D113" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C114" t="s">
         <v>7</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="E114" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C115" t="s">
         <v>7</v>
       </c>
       <c r="D115" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C116" t="s">
         <v>7</v>
       </c>
       <c r="D116" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C117" t="s">
         <v>7</v>
       </c>
       <c r="D117" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B118" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C118" t="s">
         <v>7</v>
       </c>
       <c r="D118" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B119" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C119" t="s">
         <v>7</v>
       </c>
       <c r="D119" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E119" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B120" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C120" t="s">
         <v>7</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B121" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C121" t="s">
         <v>7</v>
       </c>
       <c r="D121" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C122" t="s">
         <v>7</v>
       </c>
       <c r="D122" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C123" t="s">
         <v>7</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B124" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C124" t="s">
         <v>7</v>
       </c>
       <c r="D124" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B125" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C125" t="s">
         <v>7</v>
       </c>
       <c r="D125" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C126" t="s">
         <v>7</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B127" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C127" t="s">
         <v>7</v>
       </c>
       <c r="D127" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="E127" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C128" t="s">
         <v>7</v>
       </c>
       <c r="D128" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B129" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C129" t="s">
         <v>7</v>
       </c>
       <c r="D129" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B130" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C130" t="s">
         <v>7</v>
       </c>
       <c r="D130" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C131" t="s">
         <v>7</v>
       </c>
       <c r="D131" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E131" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C132" t="s">
         <v>7</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E132" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B133" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C133" t="s">
         <v>7</v>
       </c>
       <c r="D133" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B134" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C134" t="s">
         <v>7</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B135" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C135" t="s">
         <v>7</v>
       </c>
       <c r="D135" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E135" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B136" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C136" t="s">
         <v>7</v>
       </c>
       <c r="D136" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="E136" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C137" t="s">
         <v>7</v>
@@ -3251,10 +3257,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B138" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C138" t="s">
         <v>7</v>
@@ -3268,16 +3274,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B139" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C139" t="s">
         <v>7</v>
       </c>
       <c r="D139" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E139" t="s">
         <v>13</v>
@@ -3285,78 +3291,78 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C140" t="s">
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C141" t="s">
         <v>7</v>
       </c>
       <c r="D141" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="E141" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B142" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C142" t="s">
         <v>7</v>
       </c>
       <c r="D142" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E142" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B143" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C143" t="s">
         <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E143" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C144" t="s">
         <v>7</v>
@@ -3370,10 +3376,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B145" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C145" t="s">
         <v>7</v>
@@ -3387,16 +3393,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B146" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C146" t="s">
         <v>7</v>
       </c>
       <c r="D146" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E146" t="s">
         <v>13</v>
@@ -3404,716 +3410,1243 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B147" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C147" t="s">
         <v>7</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B148" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C148" t="s">
         <v>7</v>
       </c>
       <c r="D148" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="E148" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B149" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C149" t="s">
         <v>7</v>
       </c>
       <c r="D149" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="E149" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B150" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C150" t="s">
         <v>7</v>
       </c>
       <c r="D150" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E150" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="C151" t="s">
         <v>7</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="E151" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="C152" t="s">
         <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E152" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C153" t="s">
         <v>7</v>
       </c>
       <c r="D153" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B154" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C154" t="s">
         <v>7</v>
       </c>
       <c r="D154" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B155" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C155" t="s">
         <v>7</v>
       </c>
       <c r="D155" t="s">
-        <v>148</v>
+        <v>12</v>
       </c>
       <c r="E155" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B156" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C156" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D156" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E156" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B157" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C157" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B158" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C158" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D158" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="E158" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B159" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C159" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B160" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C160" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D160" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C161" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D161" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="E161" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B162" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C162" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="E162" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B163" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C163" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D163" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E163" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C164" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D164" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E164" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B165" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C165" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D165" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E165" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B166" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C166" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B167" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C167" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D167" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="E167" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B168" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C168" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D168" t="s">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>156</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B169" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C169" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D169" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B170" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C170" t="s">
         <v>7</v>
       </c>
       <c r="D170" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E170" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B171" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C171" t="s">
         <v>7</v>
       </c>
       <c r="D171" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E171" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B172" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C172" t="s">
         <v>7</v>
       </c>
       <c r="D172" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E172" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B173" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C173" t="s">
         <v>7</v>
       </c>
       <c r="D173" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="E173" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B174" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="C174" t="s">
         <v>7</v>
       </c>
       <c r="D174" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="E174" t="s">
-        <v>9</v>
+        <v>145</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B175" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="C175" t="s">
         <v>7</v>
       </c>
       <c r="D175" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="E175" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B176" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C176" t="s">
         <v>7</v>
       </c>
       <c r="D176" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B177" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C177" t="s">
         <v>7</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B178" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C178" t="s">
         <v>7</v>
       </c>
       <c r="D178" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E178" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B179" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C179" t="s">
         <v>7</v>
       </c>
       <c r="D179" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B180" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C180" t="s">
         <v>7</v>
       </c>
       <c r="D180" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="C181" t="s">
         <v>7</v>
       </c>
       <c r="D181" t="s">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="E181" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B182" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C182" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D182" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E182" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B183" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D183" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E183" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B184" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C184" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B185" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C185" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D185" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B186" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C186" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D186" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E186" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B187" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C187" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="D187" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="E187" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>152</v>
+      </c>
+      <c r="B188" t="s">
+        <v>153</v>
+      </c>
+      <c r="C188" t="s">
+        <v>154</v>
+      </c>
+      <c r="D188" t="s">
+        <v>157</v>
+      </c>
+      <c r="E188" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>152</v>
+      </c>
+      <c r="B189" t="s">
+        <v>153</v>
+      </c>
+      <c r="C189" t="s">
+        <v>154</v>
+      </c>
+      <c r="D189" t="s">
+        <v>159</v>
+      </c>
+      <c r="E189" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>161</v>
+      </c>
+      <c r="B190" t="s">
+        <v>162</v>
+      </c>
+      <c r="C190" t="s">
+        <v>154</v>
+      </c>
+      <c r="D190" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>161</v>
+      </c>
+      <c r="B191" t="s">
+        <v>162</v>
+      </c>
+      <c r="C191" t="s">
+        <v>154</v>
+      </c>
+      <c r="D191" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>161</v>
+      </c>
+      <c r="B192" t="s">
+        <v>162</v>
+      </c>
+      <c r="C192" t="s">
+        <v>154</v>
+      </c>
+      <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>161</v>
+      </c>
+      <c r="B193" t="s">
+        <v>162</v>
+      </c>
+      <c r="C193" t="s">
+        <v>154</v>
+      </c>
+      <c r="D193" t="s">
+        <v>33</v>
+      </c>
+      <c r="E193" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>161</v>
+      </c>
+      <c r="B194" t="s">
+        <v>162</v>
+      </c>
+      <c r="C194" t="s">
+        <v>154</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>161</v>
+      </c>
+      <c r="B195" t="s">
+        <v>162</v>
+      </c>
+      <c r="C195" t="s">
+        <v>154</v>
+      </c>
+      <c r="D195" t="s">
+        <v>163</v>
+      </c>
+      <c r="E195" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>161</v>
+      </c>
+      <c r="B196" t="s">
+        <v>162</v>
+      </c>
+      <c r="C196" t="s">
+        <v>154</v>
+      </c>
+      <c r="D196" t="s">
+        <v>165</v>
+      </c>
+      <c r="E196" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>161</v>
+      </c>
+      <c r="B197" t="s">
+        <v>162</v>
+      </c>
+      <c r="C197" t="s">
+        <v>154</v>
+      </c>
+      <c r="D197" t="s">
+        <v>159</v>
+      </c>
+      <c r="E197" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>166</v>
+      </c>
+      <c r="B198" t="s">
+        <v>167</v>
+      </c>
+      <c r="C198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" t="s">
+        <v>8</v>
+      </c>
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>166</v>
+      </c>
+      <c r="B199" t="s">
+        <v>167</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>10</v>
+      </c>
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>166</v>
+      </c>
+      <c r="B200" t="s">
+        <v>167</v>
+      </c>
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>28</v>
+      </c>
+      <c r="E200" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>166</v>
+      </c>
+      <c r="B201" t="s">
+        <v>167</v>
+      </c>
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" t="s">
+        <v>24</v>
+      </c>
+      <c r="E201" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>166</v>
+      </c>
+      <c r="B202" t="s">
+        <v>167</v>
+      </c>
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" t="s">
+        <v>26</v>
+      </c>
+      <c r="E202" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>168</v>
+      </c>
+      <c r="B203" t="s">
         <v>169</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" t="s">
+        <v>8</v>
+      </c>
+      <c r="E203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>168</v>
+      </c>
+      <c r="B204" t="s">
+        <v>169</v>
+      </c>
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>168</v>
+      </c>
+      <c r="B205" t="s">
+        <v>169</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" t="s">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>168</v>
+      </c>
+      <c r="B206" t="s">
+        <v>169</v>
+      </c>
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" t="s">
+        <v>33</v>
+      </c>
+      <c r="E206" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>168</v>
+      </c>
+      <c r="B207" t="s">
+        <v>169</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>168</v>
+      </c>
+      <c r="B208" t="s">
+        <v>169</v>
+      </c>
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" t="s">
+        <v>20</v>
+      </c>
+      <c r="E208" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>168</v>
+      </c>
+      <c r="B209" t="s">
+        <v>169</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>38</v>
+      </c>
+      <c r="E209" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>168</v>
+      </c>
+      <c r="B210" t="s">
+        <v>169</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" t="s">
+        <v>40</v>
+      </c>
+      <c r="E210" t="s">
         <v>170</v>
       </c>
-      <c r="C188" t="s">
-        <v>7</v>
-      </c>
-      <c r="D188" t="s">
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>171</v>
+      </c>
+      <c r="B211" t="s">
+        <v>172</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>8</v>
+      </c>
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>171</v>
+      </c>
+      <c r="B212" t="s">
+        <v>172</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>10</v>
+      </c>
+      <c r="E212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>171</v>
+      </c>
+      <c r="B213" t="s">
+        <v>172</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>12</v>
+      </c>
+      <c r="E213" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>171</v>
+      </c>
+      <c r="B214" t="s">
+        <v>172</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>33</v>
+      </c>
+      <c r="E214" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>171</v>
+      </c>
+      <c r="B215" t="s">
+        <v>172</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
         <v>18</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E215" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>171</v>
+      </c>
+      <c r="B216" t="s">
+        <v>172</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" t="s">
+        <v>38</v>
+      </c>
+      <c r="E216" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>171</v>
+      </c>
+      <c r="B217" t="s">
+        <v>172</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>40</v>
+      </c>
+      <c r="E217" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>171</v>
+      </c>
+      <c r="B218" t="s">
+        <v>172</v>
+      </c>
+      <c r="C218" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" t="s">
+        <v>173</v>
+      </c>
+      <c r="E218" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>171</v>
+      </c>
+      <c r="B219" t="s">
+        <v>172</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>20</v>
+      </c>
+      <c r="E219" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/input/youtube-tests.xlsx
+++ b/input/youtube-tests.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="600" windowWidth="19815" windowHeight="7110"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ManualTestCases" state="visible" r:id="rId4"/>
+    <sheet name="ManualTestCases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="176">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -536,22 +539,27 @@
   </si>
   <si>
     <t>The browser returns to the video</t>
+  </si>
+  <si>
+    <t>Enter "playwright automation tutorial in tamil" in the search box</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -915,9 +923,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E219"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -926,7 +934,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -943,7 +951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -960,7 +968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -977,7 +985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -994,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1011,7 +1019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1028,7 +1036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1045,7 +1053,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1062,7 +1070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1079,7 +1087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1096,7 +1104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1113,7 +1121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1130,7 +1138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1147,7 +1155,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1164,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1181,7 +1189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1198,7 +1206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1215,7 +1223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1232,7 +1240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1249,7 +1257,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1283,7 +1291,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1300,7 +1308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1317,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1334,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1351,7 +1359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1368,7 +1376,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -1385,7 +1393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1402,7 +1410,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1419,7 +1427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1436,7 +1444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1453,7 +1461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -1470,7 +1478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -1504,7 +1512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -1521,7 +1529,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -1538,7 +1546,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -1555,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -1572,7 +1580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -1589,7 +1597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -1606,7 +1614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -1623,7 +1631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -1640,7 +1648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1657,7 +1665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -1674,7 +1682,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1691,7 +1699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>52</v>
       </c>
@@ -1708,7 +1716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1725,7 +1733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -1742,7 +1750,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1759,7 +1767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1776,7 +1784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1793,7 +1801,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1810,7 +1818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -1844,7 +1852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -1861,7 +1869,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -1878,7 +1886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1895,7 +1903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1912,7 +1920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -1929,7 +1937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -1946,7 +1954,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -1963,7 +1971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1980,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -1997,7 +2005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2014,7 +2022,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2031,7 +2039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -2048,7 +2056,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -2082,7 +2090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -2099,7 +2107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -2116,7 +2124,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -2133,7 +2141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -2150,7 +2158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>70</v>
       </c>
@@ -2167,7 +2175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>70</v>
       </c>
@@ -2184,7 +2192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>70</v>
       </c>
@@ -2201,7 +2209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>70</v>
       </c>
@@ -2218,7 +2226,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -2235,7 +2243,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>70</v>
       </c>
@@ -2252,7 +2260,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>76</v>
       </c>
@@ -2269,7 +2277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>76</v>
       </c>
@@ -2286,7 +2294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>76</v>
       </c>
@@ -2303,7 +2311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>76</v>
       </c>
@@ -2320,7 +2328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -2337,7 +2345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>76</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -2371,7 +2379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>76</v>
       </c>
@@ -2388,7 +2396,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>76</v>
       </c>
@@ -2405,7 +2413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -2422,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -2439,7 +2447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>79</v>
       </c>
@@ -2456,7 +2464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>79</v>
       </c>
@@ -2473,7 +2481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>79</v>
       </c>
@@ -2490,7 +2498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>81</v>
       </c>
@@ -2507,7 +2515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>81</v>
       </c>
@@ -2524,7 +2532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>81</v>
       </c>
@@ -2541,7 +2549,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>81</v>
       </c>
@@ -2558,7 +2566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>81</v>
       </c>
@@ -2575,7 +2583,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>81</v>
       </c>
@@ -2592,7 +2600,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>89</v>
       </c>
@@ -2609,7 +2617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -2626,7 +2634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>89</v>
       </c>
@@ -2643,7 +2651,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>89</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>89</v>
       </c>
@@ -2677,7 +2685,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -2694,7 +2702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -2711,7 +2719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>94</v>
       </c>
@@ -2728,7 +2736,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>94</v>
       </c>
@@ -2745,7 +2753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -2762,7 +2770,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -2779,7 +2787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -2796,7 +2804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>97</v>
       </c>
@@ -2813,7 +2821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>97</v>
       </c>
@@ -2830,7 +2838,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -2847,7 +2855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>97</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>99</v>
       </c>
@@ -2881,7 +2889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>99</v>
       </c>
@@ -2898,7 +2906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>99</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>99</v>
       </c>
@@ -2932,7 +2940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>99</v>
       </c>
@@ -2949,7 +2957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>99</v>
       </c>
@@ -2966,7 +2974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>99</v>
       </c>
@@ -2983,7 +2991,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>101</v>
       </c>
@@ -3000,7 +3008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>101</v>
       </c>
@@ -3017,7 +3025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>101</v>
       </c>
@@ -3034,7 +3042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>101</v>
       </c>
@@ -3051,7 +3059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>101</v>
       </c>
@@ -3068,7 +3076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>101</v>
       </c>
@@ -3085,7 +3093,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>103</v>
       </c>
@@ -3102,7 +3110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>103</v>
       </c>
@@ -3119,7 +3127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>103</v>
       </c>
@@ -3136,7 +3144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>103</v>
       </c>
@@ -3153,7 +3161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>103</v>
       </c>
@@ -3170,7 +3178,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>103</v>
       </c>
@@ -3187,7 +3195,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>103</v>
       </c>
@@ -3204,7 +3212,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>103</v>
       </c>
@@ -3221,7 +3229,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>103</v>
       </c>
@@ -3238,7 +3246,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>112</v>
       </c>
@@ -3255,7 +3263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>112</v>
       </c>
@@ -3272,7 +3280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>112</v>
       </c>
@@ -3289,7 +3297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>112</v>
       </c>
@@ -3306,7 +3314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>112</v>
       </c>
@@ -3323,7 +3331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>112</v>
       </c>
@@ -3340,7 +3348,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>112</v>
       </c>
@@ -3357,7 +3365,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>118</v>
       </c>
@@ -3374,7 +3382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -3391,7 +3399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>118</v>
       </c>
@@ -3402,13 +3410,13 @@
         <v>7</v>
       </c>
       <c r="D146" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="E146" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>118</v>
       </c>
@@ -3425,7 +3433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>118</v>
       </c>
@@ -3442,7 +3450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>118</v>
       </c>
@@ -3459,7 +3467,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>118</v>
       </c>
@@ -3476,7 +3484,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>118</v>
       </c>
@@ -3493,7 +3501,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -3510,7 +3518,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>127</v>
       </c>
@@ -3527,7 +3535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>127</v>
       </c>
@@ -3544,7 +3552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>127</v>
       </c>
@@ -3561,7 +3569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>127</v>
       </c>
@@ -3578,7 +3586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>127</v>
       </c>
@@ -3595,7 +3603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>127</v>
       </c>
@@ -3612,7 +3620,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>127</v>
       </c>
@@ -3629,7 +3637,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>132</v>
       </c>
@@ -3646,7 +3654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
         <v>132</v>
       </c>
@@ -3663,7 +3671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
         <v>132</v>
       </c>
@@ -3680,7 +3688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>132</v>
       </c>
@@ -3697,7 +3705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
         <v>132</v>
       </c>
@@ -3714,7 +3722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>132</v>
       </c>
@@ -3731,7 +3739,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>132</v>
       </c>
@@ -3748,7 +3756,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>132</v>
       </c>
@@ -3765,7 +3773,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>140</v>
       </c>
@@ -3782,7 +3790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>140</v>
       </c>
@@ -3799,7 +3807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>140</v>
       </c>
@@ -3816,7 +3824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>140</v>
       </c>
@@ -3833,7 +3841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>140</v>
       </c>
@@ -3850,7 +3858,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>140</v>
       </c>
@@ -3867,7 +3875,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>140</v>
       </c>
@@ -3884,7 +3892,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>140</v>
       </c>
@@ -3901,7 +3909,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>148</v>
       </c>
@@ -3918,7 +3926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>148</v>
       </c>
@@ -3935,7 +3943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>148</v>
       </c>
@@ -3952,7 +3960,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>148</v>
       </c>
@@ -3969,7 +3977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>148</v>
       </c>
@@ -3986,7 +3994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>148</v>
       </c>
@@ -4003,7 +4011,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>152</v>
       </c>
@@ -4020,7 +4028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>152</v>
       </c>
@@ -4037,7 +4045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>152</v>
       </c>
@@ -4054,7 +4062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>152</v>
       </c>
@@ -4071,7 +4079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>152</v>
       </c>
@@ -4088,7 +4096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>152</v>
       </c>
@@ -4105,7 +4113,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>152</v>
       </c>
@@ -4122,7 +4130,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>152</v>
       </c>
@@ -4139,7 +4147,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
         <v>161</v>
       </c>
@@ -4156,7 +4164,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
         <v>161</v>
       </c>
@@ -4173,7 +4181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
         <v>161</v>
       </c>
@@ -4190,7 +4198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
         <v>161</v>
       </c>
@@ -4207,7 +4215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
         <v>161</v>
       </c>
@@ -4224,7 +4232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
         <v>161</v>
       </c>
@@ -4241,7 +4249,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
         <v>161</v>
       </c>
@@ -4258,7 +4266,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
         <v>161</v>
       </c>
@@ -4275,7 +4283,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
         <v>166</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
         <v>166</v>
       </c>
@@ -4309,7 +4317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
         <v>166</v>
       </c>
@@ -4326,7 +4334,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
         <v>166</v>
       </c>
@@ -4343,7 +4351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
         <v>166</v>
       </c>
@@ -4360,7 +4368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
         <v>168</v>
       </c>
@@ -4377,7 +4385,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
         <v>168</v>
       </c>
@@ -4394,7 +4402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
         <v>168</v>
       </c>
@@ -4411,7 +4419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
         <v>168</v>
       </c>
@@ -4428,7 +4436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
         <v>168</v>
       </c>
@@ -4445,7 +4453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
         <v>168</v>
       </c>
@@ -4462,7 +4470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
         <v>168</v>
       </c>
@@ -4479,7 +4487,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
         <v>168</v>
       </c>
@@ -4496,7 +4504,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
         <v>171</v>
       </c>
@@ -4513,7 +4521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>171</v>
       </c>
@@ -4530,7 +4538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
         <v>171</v>
       </c>
@@ -4547,7 +4555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
         <v>171</v>
       </c>
@@ -4564,7 +4572,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
         <v>171</v>
       </c>
@@ -4581,7 +4589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
         <v>171</v>
       </c>
@@ -4598,7 +4606,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
         <v>171</v>
       </c>
@@ -4615,7 +4623,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
         <v>171</v>
       </c>
@@ -4632,7 +4640,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
         <v>171</v>
       </c>
@@ -4651,6 +4659,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>